--- a/results/monthly_investor_report_2026-09-04.xlsx
+++ b/results/monthly_investor_report_2026-09-04.xlsx
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -689,7 +689,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 65.78/100</t>
+          <t>Güven Puanı: 69.28/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -969,25 +969,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1181200984536789</v>
+        <v>0.1181201156992633</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>11812.00984536789</v>
+        <v>11812.01156992633</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0493707647628267</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>583.1679594518513</v>
+        <v>583.1680445946204</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>407.6805421103582</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>367.6046449578748</v>
+        <v>367.6046449578747</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.9179332953036716</v>
+        <v>0.9179332953036691</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -1012,25 +1012,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1162103976391515</v>
+        <v>0.1162104029062462</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>11621.03976391515</v>
+        <v>11621.04029062462</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0354565735575836</v>
+        <v>0.0354565230645036</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>412.0422512048614</v>
+        <v>412.0416830980574</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>222.7267152921616</v>
+        <v>222.7267044310998</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>195.6263790882017</v>
+        <v>195.626377797947</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3916429734763007</v>
+        <v>0.3916423897956006</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1053,25 +1053,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1035522320007947</v>
+        <v>0.103552179816356</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>10355.22320007947</v>
+        <v>10355.2179816356</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0485933210137139</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>503.1969118116162</v>
+        <v>503.1944315486014</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>435.9527626100879</v>
+        <v>435.9526732114516</v>
       </c>
       <c r="I22" s="8" t="n">
         <v>394.9625</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.9718707208701305</v>
+        <v>0.9718664202742769</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09631036101676975</v>
+        <v>0.0963103810806922</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9631.036101676975</v>
+        <v>9631.03810806922</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.09195747824944769</v>
+        <v>0.0919574997942756</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>885.645792839606</v>
+        <v>885.6461848414358</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>423.9524909303481</v>
+        <v>423.9524992951275</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>364.6187335307732</v>
+        <v>364.6187335307733</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.510815807389788</v>
+        <v>1.510816161360639</v>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.0658069108896053</v>
+        <v>0.06580692049744219</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>6580.691088960531</v>
+        <v>6580.692049744219</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0.0349441231528639</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>229.9564798435908</v>
+        <v>229.9565134173344</v>
       </c>
       <c r="H24" s="8" t="n">
         <v>101.579767266653</v>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>49999.99999999999</v>
+        <v>50000</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1449,25 +1449,25 @@
         <v>215.1000061035156</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0905328984785914</v>
+        <v>-0.09053290447698591</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0354565735575836</v>
+        <v>0.0354565230645036</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0.1259383002873109</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>195.6263790882017</v>
+        <v>195.626377797947</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>222.7267152921616</v>
+        <v>222.7267044310998</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>242.1893352639826</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>195.6263790882017</v>
+        <v>195.626377797947</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
         <v>0.0493707647628267</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.2407264600600418</v>
+        <v>0.2407265379940244</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>377.0949406620862</v>
@@ -1521,10 +1521,10 @@
         <v>407.6805421103582</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>482.0222297333262</v>
+        <v>482.0222600106785</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>367.6046449578748</v>
+        <v>367.6046449578747</v>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="M9" s="14" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N9" s="14" t="inlineStr">
         <is>
@@ -1566,19 +1566,19 @@
         <v>0.0079654248712648</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0485933210137139</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.0892150917049894</v>
+        <v>0.0892150802528868</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>419.0616253902284</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>435.9527626100879</v>
+        <v>435.9526732114516</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>452.8411743763493</v>
+        <v>452.8411696151377</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>394.9625</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="M10" s="14" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N10" s="14" t="inlineStr">
         <is>
@@ -1620,25 +1620,25 @@
         <v>92.59999847412109</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.077838466384963</v>
+        <v>-0.07783841193174081</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>0.0224111679198997</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.094045958010278</v>
+        <v>0.0940460207708569</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>85.3921566056456</v>
+        <v>85.39216164801388</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>94.67527258930708</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>101.3086540423701</v>
+        <v>101.3086598539996</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>85.3921566056456</v>
+        <v>85.39216164801388</v>
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="M11" s="17" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
@@ -1677,25 +1677,25 @@
         <v>37.20000076293945</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.0609999645366716</v>
+        <v>-0.061000020827669</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>-0.0367800783516739</v>
+        <v>-0.0367800335642668</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0.0704910572228887</v>
+        <v>0.070491024415195</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>34.93080203563599</v>
+        <v>34.93079994161084</v>
       </c>
       <c r="I12" s="21" t="n">
-        <v>35.83178182019621</v>
+        <v>35.83178348628779</v>
       </c>
       <c r="J12" s="21" t="n">
-        <v>39.82226814541132</v>
+        <v>39.82226692496509</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>34.93080203563599</v>
+        <v>34.93079994161084</v>
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="M12" s="20" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
@@ -1734,25 +1734,25 @@
         <v>71.84999847412109</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.1210647833847655</v>
+        <v>-0.1210647605252412</v>
       </c>
       <c r="F13" s="22" t="n">
         <v>-0.031845613590586</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.0678617521643783</v>
+        <v>0.0678617289923662</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>63.15149397265589</v>
+        <v>63.15149561511268</v>
       </c>
       <c r="I13" s="21" t="n">
         <v>69.56189118623004</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>76.72586526358286</v>
+        <v>76.72586359867383</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>63.15149397265589</v>
+        <v>63.15149561511268</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="M13" s="20" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
@@ -1794,22 +1794,22 @@
         <v>0.002524799493457</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>0.09195747824944769</v>
+        <v>0.0919574997942756</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.1760202663201471</v>
+        <v>0.1760203643556419</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>389.2302534033346</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>423.9524909303481</v>
+        <v>423.9524992951275</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>456.5898683987971</v>
+        <v>456.589906461078</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>364.6187335307732</v>
+        <v>364.6187335307733</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="M14" s="14" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N14" s="14" t="inlineStr">
         <is>
@@ -1851,19 +1851,19 @@
         <v>-0.0371959299442395</v>
       </c>
       <c r="F15" s="19" t="n">
-        <v>0.0233118944998451</v>
+        <v>0.0233118283326481</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>0.1272217020935506</v>
+        <v>0.1272216922975995</v>
       </c>
       <c r="H15" s="18" t="n">
         <v>126.5124489288372</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>134.4631766914795</v>
+        <v>134.4631679971102</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>148.1169247750773</v>
+        <v>148.1169234878894</v>
       </c>
       <c r="K15" s="18" t="n">
         <v>124.8299942016602</v>
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="M15" s="17" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N15" s="17" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="M16" s="20" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>98.15000152587891</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>0.0159447965491297</v>
+        <v>0.0159447519982732</v>
       </c>
       <c r="F17" s="16" t="n">
         <v>0.0349441231528639</v>
@@ -1971,7 +1971,7 @@
         <v>0.0633663517413753</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>99.71498333150582</v>
+        <v>99.71497895883918</v>
       </c>
       <c r="I17" s="15" t="n">
         <v>101.579767266653</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="M17" s="14" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
@@ -2019,25 +2019,25 @@
         <v>274.25</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>-0.0919187004373557</v>
+        <v>-0.0919187463392733</v>
       </c>
       <c r="F18" s="25" t="n">
-        <v>-0.0127046702754232</v>
+        <v>-0.0127047496231476</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>0.0358074491049085</v>
+        <v>0.035807354318896</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>249.0412964050552</v>
+        <v>249.0412838164543</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>270.7657441769652</v>
+        <v>270.7657224158518</v>
       </c>
       <c r="J18" s="24" t="n">
-        <v>284.0701929170212</v>
+        <v>284.0701669219572</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>249.0412964050552</v>
+        <v>249.0412838164543</v>
       </c>
       <c r="L18" s="23" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="M18" s="23" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
       <c r="N18" s="23" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0190914915961079</v>
+        <v>0.0190914915961077</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0354565735575836</v>
+        <v>0.0354565230645036</v>
       </c>
     </row>
     <row r="5">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="J5" s="16" t="n">
-        <v>0.026892348831564</v>
+        <v>0.0268923488315641</v>
       </c>
       <c r="K5" s="16" t="n">
         <v>0.0493707647628267</v>
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.0190904094969909</v>
+        <v>0.019090409496991</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.0485935360435065</v>
+        <v>0.0485933210137139</v>
       </c>
     </row>
     <row r="7">
@@ -2389,7 +2389,7 @@
         <v>0.0225289601725182</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>-0.0367800783516739</v>
+        <v>-0.0367800335642668</v>
       </c>
     </row>
     <row r="9">
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="J9" s="22" t="n">
-        <v>0.0235158526951286</v>
+        <v>0.0235158526951287</v>
       </c>
       <c r="K9" s="22" t="n">
         <v>-0.031845613590586</v>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.0304330540492296</v>
+        <v>0.0304330540492295</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>0.09195747824944769</v>
+        <v>0.0919574997942756</v>
       </c>
     </row>
     <row r="11">
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="J11" s="19" t="n">
-        <v>0.0166997058172155</v>
+        <v>0.0166997058172156</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>0.0233118944998451</v>
+        <v>0.0233118283326481</v>
       </c>
     </row>
     <row r="12">
@@ -2647,7 +2647,7 @@
         <v>0.0189257716431987</v>
       </c>
       <c r="K14" s="27" t="n">
-        <v>0.0258271702581398</v>
+        <v>0.0258271723736069</v>
       </c>
     </row>
     <row r="15">
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="J15" s="25" t="n">
-        <v>0.0231990748681045</v>
+        <v>0.0231990748681046</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>-0.0127046702754232</v>
+        <v>-0.0127047496231476</v>
       </c>
     </row>
     <row r="16">
@@ -2819,7 +2819,7 @@
         <v>0.0155382958378264</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.08996540449809751</v>
+        <v>0.08996539672856251</v>
       </c>
     </row>
     <row r="19">
@@ -2862,7 +2862,7 @@
         <v>0.0127081504930393</v>
       </c>
       <c r="K19" s="27" t="n">
-        <v>0.0999999916062814</v>
+        <v>0.1000000839371915</v>
       </c>
     </row>
     <row r="20">
@@ -2938,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3057,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,7 +3308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14151.599609375</v>
+        <v>14405.2998046875</v>
       </c>
     </row>
     <row r="5">
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13362.80402832031</v>
+        <v>13381.18752929687</v>
       </c>
     </row>
     <row r="6">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>65.78</v>
+        <v>69.28</v>
       </c>
     </row>
     <row r="9">
@@ -3433,7 +3433,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-08 06:37</t>
+          <t>Son Güncelleme: 2026-09-09 06:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3510,7 +3510,7 @@
         <v>-19838.29062106635</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>11314225.18217773</v>
+        <v>11489854.14120302</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>0.0225044067881641</v>
@@ -3540,7 +3540,7 @@
         <v>267029.7336462075</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>11314225.18217773</v>
+        <v>11489854.14120302</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>0.0225044067881641</v>
@@ -3570,7 +3570,7 @@
         <v>941159.3549911883</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>11314225.18217773</v>
+        <v>11489854.14120302</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0.0225044067881641</v>
@@ -3600,7 +3600,7 @@
         <v>1628.565106133465</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>11314225.18217773</v>
+        <v>11489854.14120302</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>0.0225044067881641</v>
@@ -3630,7 +3630,7 @@
         <v>-158444.7897232156</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>11314225.18217773</v>
+        <v>11489854.14120302</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>0.0225044067881641</v>
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>11314225.18217773</v>
+        <v>11489854.14120302</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>0.0225044067881641</v>
